--- a/Dev_GNC/TableData/PawnDataTable.xlsx
+++ b/Dev_GNC/TableData/PawnDataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityProjects\CardGame\CardGameTable\Table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealProjects\ProjectGNC\Dev_GNC\TableData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB326060-F9C4-4217-BDDB-63606AB655A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43C753D-F4ED-4B60-B4AA-94998DC3E897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PawnData" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>id</t>
   </si>
@@ -55,39 +55,21 @@
     <t>sight</t>
   </si>
   <si>
-    <t>prefabPath</t>
-  </si>
-  <si>
     <t>pawn_scout</t>
   </si>
   <si>
     <t>SCOUT</t>
   </si>
   <si>
-    <t>pawn_assult</t>
-  </si>
-  <si>
-    <t>ASSULT</t>
-  </si>
-  <si>
-    <t>Prefabs/Actor/Pawn/Pawn_Assult</t>
-  </si>
-  <si>
     <t>pawn_heavy</t>
   </si>
   <si>
     <t>HEAVY</t>
   </si>
   <si>
-    <t>Prefabs/Actor/Pawn/Pawn_Heavy</t>
-  </si>
-  <si>
     <t>SPECIALIST</t>
   </si>
   <si>
-    <t>Prefabs/Actor/Pawn/Pawn_Specialist</t>
-  </si>
-  <si>
     <t>pawn_specialist</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -95,10 +77,6 @@
     <t>text_pawn_name_scout</t>
   </si>
   <si>
-    <t>text_pawn_name_assult</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>text_pawn_name_heavy</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -119,19 +97,23 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Prefabs/Actor/Pawn/Pawn_Scout</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Actor/Pawn/Pawn_Recruit</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>ammo</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>accuracy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pawn_assault</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASSAULT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_pawn_name_assault</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -402,10 +384,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -440,27 +422,24 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E2" s="1">
         <v>10</v>
@@ -489,22 +468,19 @@
       <c r="M2" s="1">
         <v>0</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>31</v>
-      </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="E3" s="1">
         <v>10</v>
@@ -533,22 +509,19 @@
       <c r="M3" s="1">
         <v>0</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>30</v>
-      </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E4" s="1">
         <v>10</v>
@@ -577,22 +550,19 @@
       <c r="M4" s="1">
         <v>0</v>
       </c>
-      <c r="N4" s="1" t="s">
-        <v>16</v>
-      </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E5" s="1">
         <v>15</v>
@@ -621,22 +591,19 @@
       <c r="M5" s="1">
         <v>0</v>
       </c>
-      <c r="N5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1">
         <v>10</v>
@@ -664,9 +631,6 @@
       </c>
       <c r="M6" s="1">
         <v>0</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Dev_GNC/TableData/PawnDataTable.xlsx
+++ b/Dev_GNC/TableData/PawnDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealProjects\ProjectGNC\Dev_GNC\TableData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43C753D-F4ED-4B60-B4AA-94998DC3E897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E058543-FE94-415A-8460-B094B35604D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39180" yWindow="2460" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PawnData" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
     <t>idAlias</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>classType</t>
   </si>
   <si>
@@ -114,6 +111,10 @@
   </si>
   <si>
     <t>text_pawn_name_assault</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>nameAlias</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -395,37 +396,37 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -433,13 +434,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="E2" s="1">
         <v>10</v>
@@ -474,13 +475,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E3" s="1">
         <v>10</v>
@@ -515,13 +516,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="E4" s="1">
         <v>10</v>
@@ -556,13 +557,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="E5" s="1">
         <v>15</v>
@@ -597,13 +598,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="1">
         <v>10</v>
